--- a/public/templates/ttn_2026.xlsx
+++ b/public/templates/ttn_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
   <si>
     <t>Приложение 9</t>
   </si>
@@ -3263,7 +3263,9 @@
       <c r="G39" s="127"/>
       <c r="H39" s="127"/>
       <c r="I39" s="127"/>
-      <c r="J39" s="99"/>
+      <c r="J39" s="99" t="s">
+        <v>58</v>
+      </c>
       <c r="K39" s="99"/>
       <c r="L39" s="128"/>
       <c r="M39" s="126" t="s">
@@ -3273,7 +3275,9 @@
       <c r="O39" s="127"/>
       <c r="P39" s="127"/>
       <c r="Q39" s="127"/>
-      <c r="R39" s="99"/>
+      <c r="R39" s="99" t="s">
+        <v>58</v>
+      </c>
       <c r="S39" s="99"/>
       <c r="T39" s="126"/>
       <c r="U39" s="127"/>

--- a/public/templates/ttn_2026.xlsx
+++ b/public/templates/ttn_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="145">
   <si>
     <t>Приложение 9</t>
   </si>
@@ -482,6 +482,15 @@
   </si>
   <si>
     <t>Подпись таксировщика</t>
+  </si>
+  <si>
+    <t>{vehicle}</t>
+  </si>
+  <si>
+    <t>{driver}</t>
+  </si>
+  <si>
+    <t>{stamp_here}</t>
   </si>
 </sst>
 </file>
@@ -2528,7 +2537,9 @@
       <c r="X9" s="33"/>
     </row>
     <row r="10" ht="13.8" customHeight="1" spans="15:24" x14ac:dyDescent="0.25">
-      <c r="O10" s="19"/>
+      <c r="O10" s="19" t="s">
+        <v>142</v>
+      </c>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
@@ -2559,7 +2570,9 @@
       <c r="L11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="39"/>
+      <c r="N11" s="39" t="s">
+        <v>143</v>
+      </c>
       <c r="O11" s="39"/>
       <c r="P11" s="37"/>
       <c r="Q11" s="8" t="s">
@@ -3509,7 +3522,9 @@
     <row r="47" ht="13.8" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B47" s="127"/>
       <c r="C47" s="127"/>
-      <c r="D47" s="127"/>
+      <c r="D47" s="127" t="s">
+        <v>144</v>
+      </c>
       <c r="E47" s="127"/>
       <c r="F47" s="127"/>
       <c r="G47" s="127"/>
